--- a/astro-site/public/dl/hotel-checklist-templates/19-cash-drawer-opening-closing.xlsx
+++ b/astro-site/public/dl/hotel-checklist-templates/19-cash-drawer-opening-closing.xlsx
@@ -1056,7 +1056,7 @@
     <row r="48" ht="48" customHeight="1">
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>▸ Order of use: shop → register. Each file covers one level: the shop file marks the MILESTONE (turn on, open, close) and the cash file carries the MONEY. If a task shows up in both, it's on purpose: one is the milestone and the other the detail.</t>
+          <t>▸ Order of use: rounds → cash drawer. Each file covers one level: the rounds file marks the MILESTONE (turn on, open, close) and the cash file carries the MONEY. If a task shows up in both, it's on purpose: one is the milestone and the other the detail.</t>
         </is>
       </c>
     </row>
